--- a/DRAGO/Agosto/EXPENSAS-Agosto.xlsx
+++ b/DRAGO/Agosto/EXPENSAS-Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\DRAGO\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\DRAGO\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84B3410-E9D7-4E0A-8DD6-238DC6E2563A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D19E67-4906-4CFB-9541-F4C435876901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="extraordinarias" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$14</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="94">
   <si>
     <t>UF</t>
   </si>
@@ -298,13 +298,16 @@
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Período julio 2025</t>
-  </si>
-  <si>
-    <t>Vto. 14/08</t>
-  </si>
-  <si>
-    <t>LIQUIDACIÓN EXPENSAS JULIO 2025</t>
+    <t>Vto. 15/09</t>
+  </si>
+  <si>
+    <t>LIQUIDACIÓN EXPENSAS AGOSTO 2025</t>
+  </si>
+  <si>
+    <t>Período AGOSTO 2025</t>
+  </si>
+  <si>
+    <t>Julio Doartero - Arreglo de portero</t>
   </si>
 </sst>
 </file>
@@ -312,11 +315,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -867,9 +870,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -880,7 +883,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -903,14 +906,14 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -928,7 +931,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -936,10 +939,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -948,13 +951,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -962,11 +965,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -976,7 +979,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -999,7 +1002,7 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1007,7 +1010,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1017,14 +1020,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1039,9 +1042,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1049,17 +1052,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1105,8 +1105,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1475,17 +1479,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:H55"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>21</v>
       </c>
@@ -1493,43 +1497,43 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="25"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
         <v>39</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1537,7 +1541,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -1545,37 +1549,37 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="86" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="77"/>
       <c r="C16" s="119"/>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="77" t="s">
         <v>54</v>
       </c>
       <c r="B17" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="84">
+      <c r="C17" s="137">
         <v>41718</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="14"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="77" t="s">
         <v>71</v>
       </c>
@@ -1586,34 +1590,34 @@
       <c r="D18" s="49"/>
       <c r="E18" s="14"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="77" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="84">
-        <v>15030.94</v>
+      <c r="C19" s="137">
+        <v>15348.19</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="14"/>
       <c r="F19" s="18"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="77" t="s">
         <v>35</v>
       </c>
       <c r="B20" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="121">
-        <v>145207.69</v>
+      <c r="C20" s="138">
+        <v>148086.38</v>
       </c>
       <c r="D20" s="49"/>
       <c r="F20" s="14"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="77" t="s">
         <v>36</v>
       </c>
@@ -1629,27 +1633,27 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="90"/>
       <c r="B22" s="91"/>
       <c r="C22" s="64">
         <f>SUM(C17:C21)</f>
-        <v>250023.84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>253219.78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="86" t="s">
         <v>37</v>
       </c>
       <c r="B23" s="89"/>
       <c r="C23" s="119"/>
     </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="77" t="s">
         <v>72</v>
       </c>
       <c r="B24" s="92" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C24" s="84">
         <f>65200+65200*5%</f>
@@ -1657,214 +1661,224 @@
       </c>
       <c r="F24" s="22"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="77" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="92"/>
+      <c r="C25" s="137">
+        <v>85000</v>
+      </c>
+      <c r="F25" s="22"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="92"/>
-      <c r="C25" s="84">
+      <c r="B26" s="92"/>
+      <c r="C26" s="84">
         <v>33650</v>
       </c>
-      <c r="F25" s="22"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="77" t="s">
+      <c r="F26" s="22"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="B26" s="89"/>
-      <c r="C26" s="85"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="22"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="90"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="64">
-        <f>SUM(C23:C26)</f>
-        <v>102110</v>
-      </c>
+      <c r="B27" s="89"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="14"/>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="80" t="s">
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="90"/>
+      <c r="B28" s="91"/>
+      <c r="C28" s="64">
+        <f>SUM(C23:C27)</f>
+        <v>187110</v>
+      </c>
+      <c r="F28" s="22"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="80"/>
-      <c r="C28" s="93">
-        <f>+C27+C22</f>
-        <v>352133.83999999997</v>
-      </c>
-      <c r="F28" s="22"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C29" s="65"/>
+      <c r="B29" s="80"/>
+      <c r="C29" s="93">
+        <f>+C28+C22</f>
+        <v>440329.78</v>
+      </c>
       <c r="F29" s="22"/>
     </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
-        <v>47</v>
-      </c>
+    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C30" s="65"/>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="77"/>
-      <c r="B31" s="77"/>
-      <c r="C31" s="84"/>
+    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="65"/>
       <c r="F31" s="22"/>
     </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="77"/>
       <c r="B32" s="77"/>
-      <c r="C32" s="85"/>
+      <c r="C32" s="84"/>
       <c r="F32" s="22"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="77"/>
       <c r="B33" s="77"/>
       <c r="C33" s="85"/>
       <c r="F33" s="22"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C34" s="67"/>
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="77"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="85"/>
       <c r="F34" s="22"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C35" s="67"/>
+      <c r="F35" s="22"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="24">
-        <f>+C31+C32+C33+C34</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="14"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="35" t="s">
+      <c r="B36" s="23"/>
+      <c r="C36" s="24">
+        <f>+C32+C33+C34+C35</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="14"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="35"/>
-      <c r="C37" s="36">
-        <f>+C35+C28</f>
-        <v>352133.83999999997</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="B38" s="35"/>
+      <c r="C38" s="36">
+        <f>+C36+C29</f>
+        <v>440329.78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="37" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="34"/>
-      <c r="C40" s="41">
+      <c r="B41" s="34"/>
+      <c r="C41" s="41">
         <v>330849.82114340004</v>
       </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C42" s="33">
         <f>'prorrateo '!F13</f>
         <v>391571.68980998907</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="94"/>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" s="94"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>79</v>
       </c>
-      <c r="C43" s="94">
-        <f>-(C28-C26)</f>
-        <v>-352133.83999999997</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="37" t="s">
+      <c r="C44" s="94">
+        <f>-(C29-C27)</f>
+        <v>-440329.78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B44" s="34"/>
-      <c r="C44" s="41">
-        <f>SUM(C40:C43)</f>
-        <v>370287.67095338914</v>
-      </c>
-      <c r="D44" s="6"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="19"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="20"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B45" s="34"/>
+      <c r="C45" s="41">
+        <f>SUM(C41:C44)</f>
+        <v>282091.73095338908</v>
+      </c>
+      <c r="D45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="19"/>
       <c r="B46" s="18"/>
       <c r="C46" s="20"/>
-      <c r="F46" s="95"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="19"/>
       <c r="B47" s="18"/>
       <c r="C47" s="20"/>
-    </row>
-    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="76" t="s">
+      <c r="F47" s="95"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="19"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="20"/>
+    </row>
+    <row r="49" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="B48" s="99"/>
-      <c r="C48" s="100">
+      <c r="B49" s="99"/>
+      <c r="C49" s="100">
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="77"/>
-      <c r="B49" s="77"/>
-      <c r="C49" s="83"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="80" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="77"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="83"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="78"/>
-      <c r="C50" s="79">
-        <f>SUM(C48:C49)</f>
+      <c r="B51" s="78"/>
+      <c r="C51" s="79">
+        <f>SUM(C49:C50)</f>
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="18"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="18"/>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="18"/>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="18"/>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1883,24 +1897,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" hidden="1" customWidth="1"/>
-    <col min="11" max="12" width="12.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="21"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="55" t="s">
         <v>52</v>
       </c>
@@ -1909,13 +1923,13 @@
       </c>
       <c r="G1" t="str">
         <f>'detalle y gastos'!C7</f>
-        <v>Vto. 14/08</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>Vto. 15/09</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="106" t="str">
         <f>'detalle y gastos'!B7</f>
-        <v>LIQUIDACIÓN EXPENSAS JULIO 2025</v>
+        <v>LIQUIDACIÓN EXPENSAS AGOSTO 2025</v>
       </c>
       <c r="B2" s="101"/>
       <c r="C2" s="107"/>
@@ -1932,61 +1946,61 @@
       <c r="L2" s="101"/>
       <c r="M2" s="102"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="124"/>
-      <c r="B3" s="122" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="123"/>
+      <c r="B3" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="130" t="s">
+      <c r="C3" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="131" t="s">
+      <c r="D3" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="122" t="s">
+      <c r="E3" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="128" t="s">
+      <c r="F3" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="130" t="s">
+      <c r="G3" s="129" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="128" t="s">
+      <c r="H3" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="130" t="s">
+      <c r="I3" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="132" t="s">
+      <c r="J3" s="131" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="126" t="s">
+      <c r="K3" s="125" t="s">
         <v>84</v>
       </c>
-      <c r="L3" s="126" t="s">
+      <c r="L3" s="125" t="s">
         <v>85</v>
       </c>
-      <c r="M3" s="126" t="s">
+      <c r="M3" s="125" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="125"/>
-      <c r="B4" s="123"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="127"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="124"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="126"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="103">
         <v>1</v>
       </c>
@@ -2003,7 +2017,7 @@
         <v>38916.559659999992</v>
       </c>
       <c r="F5" s="120">
-        <f>E5</f>
+        <f t="shared" ref="F5:F11" si="0">E5</f>
         <v>38916.559659999992</v>
       </c>
       <c r="G5" s="47">
@@ -2031,7 +2045,7 @@
         <v>44312.522425599993</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="103">
         <v>2</v>
       </c>
@@ -2048,15 +2062,15 @@
         <v>39238.184119999998</v>
       </c>
       <c r="F6" s="120">
-        <f>E6</f>
+        <f t="shared" si="0"/>
         <v>39238.184119999998</v>
       </c>
       <c r="G6" s="47">
-        <f t="shared" ref="G6:G12" si="0">E6-F6</f>
+        <f t="shared" ref="G6:G12" si="1">E6-F6</f>
         <v>0</v>
       </c>
       <c r="H6" s="47">
-        <f t="shared" ref="H6:H12" si="1">IF(G6&gt;0,G6*5%,0)</f>
+        <f t="shared" ref="H6:H12" si="2">IF(G6&gt;0,G6*5%,0)</f>
         <v>0</v>
       </c>
       <c r="I6" s="109">
@@ -2068,17 +2082,17 @@
         <v>42960.328479999996</v>
       </c>
       <c r="L6" s="110">
-        <f t="shared" ref="L6:L12" si="2">E6-F6+H6+K6+J6</f>
+        <f t="shared" ref="L6:L12" si="3">E6-F6+H6+K6+J6</f>
         <v>42960.328479999996</v>
       </c>
       <c r="M6" s="111">
-        <f t="shared" ref="M6:M12" si="3">L6+L6*4%</f>
+        <f t="shared" ref="M6:M12" si="4">L6+L6*4%</f>
         <v>44678.741619199995</v>
       </c>
       <c r="O6" s="118"/>
       <c r="Q6" s="117"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="103">
         <v>3</v>
       </c>
@@ -2095,15 +2109,15 @@
         <v>37630.061819999995</v>
       </c>
       <c r="F7" s="120">
-        <f>E7</f>
+        <f t="shared" si="0"/>
         <v>37630.061819999995</v>
       </c>
       <c r="G7" s="47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H7" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I7" s="109">
@@ -2115,15 +2129,15 @@
         <v>41199.65928</v>
       </c>
       <c r="L7" s="110">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>41199.65928</v>
       </c>
       <c r="M7" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>42847.6456512</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="103">
         <v>4</v>
       </c>
@@ -2140,15 +2154,15 @@
         <v>106362.93804998914</v>
       </c>
       <c r="F8" s="120">
-        <f>E8</f>
+        <f t="shared" si="0"/>
         <v>106362.93804998914</v>
       </c>
       <c r="G8" s="47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H8" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I8" s="109">
@@ -2160,15 +2174,15 @@
         <v>41199.65928</v>
       </c>
       <c r="L8" s="110">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>41199.65928</v>
       </c>
       <c r="M8" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>42847.6456512</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="103">
         <v>5</v>
       </c>
@@ -2185,15 +2199,15 @@
         <v>44062.551019999999</v>
       </c>
       <c r="F9" s="120">
-        <f>E9</f>
+        <f t="shared" si="0"/>
         <v>44062.551019999999</v>
       </c>
       <c r="G9" s="47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H9" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I9" s="109">
@@ -2205,15 +2219,15 @@
         <v>48242.336080000001</v>
       </c>
       <c r="L9" s="110">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>48242.336080000001</v>
       </c>
       <c r="M9" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>50172.029523199999</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="103">
         <v>6</v>
       </c>
@@ -2230,15 +2244,15 @@
         <v>42454.428719999996</v>
       </c>
       <c r="F10" s="120">
-        <f>E10</f>
+        <f t="shared" si="0"/>
         <v>42454.428719999996</v>
       </c>
       <c r="G10" s="47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H10" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I10" s="109">
@@ -2250,15 +2264,15 @@
         <v>46481.666879999997</v>
       </c>
       <c r="L10" s="110">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>46481.666879999997</v>
       </c>
       <c r="M10" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>48340.933555199997</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="103">
         <v>7</v>
       </c>
@@ -2275,15 +2289,15 @@
         <v>40846.306419999994</v>
       </c>
       <c r="F11" s="120">
-        <f>E11</f>
+        <f t="shared" si="0"/>
         <v>40846.306419999994</v>
       </c>
       <c r="G11" s="47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H11" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I11" s="109">
@@ -2295,15 +2309,15 @@
         <v>44720.997679999993</v>
       </c>
       <c r="L11" s="110">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>44720.997679999993</v>
       </c>
       <c r="M11" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>46509.837587199996</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="103">
         <v>8</v>
       </c>
@@ -2323,11 +2337,11 @@
         <v>42060.66</v>
       </c>
       <c r="G12" s="47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-2832.0667800000083</v>
       </c>
       <c r="H12" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I12" s="109">
@@ -2339,15 +2353,15 @@
         <v>44720.997679999993</v>
       </c>
       <c r="L12" s="110">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>41888.930899999985</v>
       </c>
       <c r="M12" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>43564.488135999985</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="112" t="s">
         <v>11</v>
       </c>
@@ -2368,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="105">
-        <f t="shared" ref="I13" si="4">SUM(I5:I12)</f>
+        <f t="shared" ref="I13" si="5">SUM(I5:I12)</f>
         <v>1</v>
       </c>
       <c r="J13" s="105">
@@ -2388,7 +2402,7 @@
         <v>363273.84414880001</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="55" t="s">
         <v>53</v>
       </c>
@@ -2396,7 +2410,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
         <v>56</v>
       </c>
@@ -2415,7 +2429,7 @@
       <c r="L17" s="56"/>
       <c r="M17" s="32"/>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
@@ -2448,7 +2462,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2475,7 +2489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <v>1</v>
       </c>
@@ -2510,7 +2524,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <v>2</v>
       </c>
@@ -2536,7 +2550,7 @@
       </c>
       <c r="J21" s="96"/>
       <c r="K21" s="45">
-        <f t="shared" ref="K21:K27" si="5">0*I21</f>
+        <f t="shared" ref="K21:K27" si="6">0*I21</f>
         <v>0</v>
       </c>
       <c r="L21" s="42"/>
@@ -2545,7 +2559,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>3</v>
       </c>
@@ -2572,7 +2586,7 @@
       </c>
       <c r="J22" s="96"/>
       <c r="K22" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L22" s="42"/>
@@ -2581,7 +2595,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>4</v>
       </c>
@@ -2604,7 +2618,7 @@
       </c>
       <c r="J23" s="96"/>
       <c r="K23" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L23" s="42"/>
@@ -2613,7 +2627,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>5</v>
       </c>
@@ -2636,7 +2650,7 @@
       </c>
       <c r="J24" s="96"/>
       <c r="K24" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L24" s="42"/>
@@ -2645,7 +2659,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>6</v>
       </c>
@@ -2668,7 +2682,7 @@
       </c>
       <c r="J25" s="96"/>
       <c r="K25" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L25" s="42"/>
@@ -2677,7 +2691,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>7</v>
       </c>
@@ -2703,7 +2717,7 @@
       </c>
       <c r="J26" s="96"/>
       <c r="K26" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L26" s="42"/>
@@ -2712,7 +2726,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>8</v>
       </c>
@@ -2738,7 +2752,7 @@
       </c>
       <c r="J27" s="96"/>
       <c r="K27" s="45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L27" s="42"/>
@@ -2747,7 +2761,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>11</v>
       </c>
@@ -2767,12 +2781,12 @@
         <v>0</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" ref="I28:K28" si="6">SUM(I20:I27)</f>
+        <f t="shared" ref="I28:K28" si="7">SUM(I20:I27)</f>
         <v>1</v>
       </c>
       <c r="J28" s="97"/>
       <c r="K28" s="40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L28" s="43"/>
@@ -2781,15 +2795,15 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="I30" s="60"/>
       <c r="J30" s="60"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="I31" s="60"/>
       <c r="J31" s="60"/>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E39" s="54"/>
     </row>
   </sheetData>
@@ -2817,39 +2831,39 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="9" width="0.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="0.109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
     <col min="12" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D1" s="58">
         <v>50000</v>
       </c>
-      <c r="H1" s="137">
+      <c r="H1" s="136">
         <v>250000</v>
       </c>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="55" t="s">
         <v>53</v>
       </c>
       <c r="B2" s="1"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="28" t="s">
         <v>68</v>
       </c>
@@ -2872,7 +2886,7 @@
       <c r="N3" s="32"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2904,18 +2918,18 @@
         <v>58</v>
       </c>
       <c r="K4" s="71"/>
-      <c r="L4" s="135" t="s">
+      <c r="L4" s="134" t="s">
         <v>74</v>
       </c>
       <c r="M4" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="133" t="s">
+      <c r="N4" s="132" t="s">
         <v>59</v>
       </c>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2939,14 +2953,14 @@
         <v>73</v>
       </c>
       <c r="K5" s="61"/>
-      <c r="L5" s="136"/>
+      <c r="L5" s="135"/>
       <c r="M5" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="134"/>
+      <c r="N5" s="133"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -2994,7 +3008,7 @@
       </c>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>2</v>
       </c>
@@ -3042,7 +3056,7 @@
       </c>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>3</v>
       </c>
@@ -3090,7 +3104,7 @@
       </c>
       <c r="P8" s="21"/>
     </row>
-    <row r="9" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>4</v>
       </c>
@@ -3138,7 +3152,7 @@
       </c>
       <c r="P9" s="21"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>5</v>
       </c>
@@ -3186,7 +3200,7 @@
       </c>
       <c r="P10" s="21"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>6</v>
       </c>
@@ -3234,7 +3248,7 @@
       </c>
       <c r="P11" s="21"/>
     </row>
-    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>7</v>
       </c>
@@ -3282,7 +3296,7 @@
       </c>
       <c r="P12" s="21"/>
     </row>
-    <row r="13" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>8</v>
       </c>
@@ -3330,7 +3344,7 @@
       </c>
       <c r="P13" s="21"/>
     </row>
-    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>

--- a/DRAGO/Agosto/EXPENSAS-Agosto.xlsx
+++ b/DRAGO/Agosto/EXPENSAS-Agosto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\DRAGO\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\DRAGO\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D19E67-4906-4CFB-9541-F4C435876901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4644C592-B604-46C0-ADA8-8A1A8107C1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="96">
   <si>
     <t>UF</t>
   </si>
@@ -214,9 +214,6 @@
     <t>Pamela</t>
   </si>
   <si>
-    <t>Nicolas</t>
-  </si>
-  <si>
     <t>Melina</t>
   </si>
   <si>
@@ -259,9 +256,6 @@
     <t>Honorarios administracion</t>
   </si>
   <si>
-    <t xml:space="preserve">Zurich Nro Poliza. 70050787 </t>
-  </si>
-  <si>
     <t>Pago efectivo</t>
   </si>
   <si>
@@ -295,9 +289,6 @@
     <t>AUMENTADOS EN JUNI 2025</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
     <t>Vto. 15/09</t>
   </si>
   <si>
@@ -308,6 +299,21 @@
   </si>
   <si>
     <t>Julio Doartero - Arreglo de portero</t>
+  </si>
+  <si>
+    <t>Mercantil Andina</t>
+  </si>
+  <si>
+    <t>No llego factura</t>
+  </si>
+  <si>
+    <t>Nos queda recuperar ua diferencia de un Aysa mal cobrado de</t>
+  </si>
+  <si>
+    <t>Guido alterini - Poda y apuntamiento palmera</t>
+  </si>
+  <si>
+    <t>Mauro</t>
   </si>
 </sst>
 </file>
@@ -315,11 +321,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -452,7 +458,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -489,6 +495,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="31">
     <border>
@@ -870,7 +882,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -883,7 +895,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -906,14 +918,14 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -931,7 +943,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -939,10 +951,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -951,13 +963,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -965,11 +977,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -979,7 +991,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1002,7 +1014,7 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1010,7 +1022,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1020,14 +1032,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1042,9 +1054,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1052,8 +1064,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1105,11 +1117,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1480,60 +1492,60 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="25"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>39</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1541,7 +1553,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -1549,80 +1561,85 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="86" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="77"/>
       <c r="C16" s="119"/>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="77" t="s">
         <v>54</v>
       </c>
       <c r="B17" s="87" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="137">
+        <v>91</v>
+      </c>
+      <c r="C17" s="84">
         <v>41718</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="14"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="77" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="88"/>
       <c r="C18" s="84">
-        <v>3567.21</v>
+        <v>4519.75</v>
       </c>
       <c r="D18" s="49"/>
       <c r="E18" s="14"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="77" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="89" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="137">
+        <v>76</v>
+      </c>
+      <c r="C19" s="84">
         <v>15348.19</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="14"/>
       <c r="F19" s="18"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H19" s="137" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="77" t="s">
         <v>35</v>
       </c>
       <c r="B20" s="89" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="138">
-        <v>148086.38</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="C20" s="138"/>
       <c r="D20" s="49"/>
       <c r="F20" s="14"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H20" s="137">
+        <f>148086-145207</f>
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="77" t="s">
         <v>36</v>
       </c>
       <c r="B21" s="89" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C21" s="84">
         <v>44500</v>
@@ -1630,60 +1647,60 @@
       <c r="D21" s="5"/>
       <c r="E21" s="14"/>
       <c r="H21" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="90"/>
       <c r="B22" s="91"/>
       <c r="C22" s="64">
         <f>SUM(C17:C21)</f>
-        <v>253219.78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+        <v>106085.94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="86" t="s">
         <v>37</v>
       </c>
       <c r="B23" s="89"/>
       <c r="C23" s="119"/>
     </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="77" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B24" s="92" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C24" s="84">
-        <f>65200+65200*5%</f>
-        <v>68460</v>
+        <f>68460+68460*5%</f>
+        <v>71883</v>
       </c>
       <c r="F24" s="22"/>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="77" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B25" s="92"/>
-      <c r="C25" s="137">
+      <c r="C25" s="84">
         <v>85000</v>
       </c>
       <c r="F25" s="22"/>
     </row>
-    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="77" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B26" s="92"/>
       <c r="C26" s="84">
-        <v>33650</v>
+        <v>78000</v>
       </c>
       <c r="F26" s="22"/>
     </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="77" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="89"/>
       <c r="C27" s="85"/>
@@ -1691,60 +1708,60 @@
       <c r="E27" s="14"/>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="90"/>
       <c r="B28" s="91"/>
       <c r="C28" s="64">
         <f>SUM(C23:C27)</f>
-        <v>187110</v>
+        <v>234883</v>
       </c>
       <c r="F28" s="22"/>
     </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B29" s="80"/>
       <c r="C29" s="93">
         <f>+C28+C22</f>
-        <v>440329.78</v>
+        <v>340968.94</v>
       </c>
       <c r="F29" s="22"/>
     </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C30" s="65"/>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="65"/>
       <c r="F31" s="22"/>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="77"/>
       <c r="B32" s="77"/>
       <c r="C32" s="84"/>
       <c r="F32" s="22"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="77"/>
       <c r="B33" s="77"/>
       <c r="C33" s="85"/>
       <c r="F33" s="22"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="77"/>
       <c r="B34" s="77"/>
       <c r="C34" s="85"/>
       <c r="F34" s="22"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C35" s="67"/>
       <c r="F35" s="22"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="23" t="s">
         <v>43</v>
       </c>
@@ -1755,102 +1772,102 @@
       </c>
       <c r="E36" s="14"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="35" t="s">
         <v>15</v>
       </c>
       <c r="B38" s="35"/>
       <c r="C38" s="36">
         <f>+C36+C29</f>
-        <v>440329.78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+        <v>340968.94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="37" t="s">
         <v>10</v>
       </c>
       <c r="B41" s="34"/>
       <c r="C41" s="41">
-        <v>330849.82114340004</v>
+        <v>370287.67095338914</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="33">
         <f>'prorrateo '!F13</f>
-        <v>391571.68980998907</v>
+        <v>331566.45097999997</v>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C43" s="94"/>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C44" s="94">
         <f>-(C29-C27)</f>
-        <v>-440329.78</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-340968.94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="37" t="s">
         <v>16</v>
       </c>
       <c r="B45" s="34"/>
       <c r="C45" s="41">
         <f>SUM(C41:C44)</f>
-        <v>282091.73095338908</v>
+        <v>360885.1819333891</v>
       </c>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="19"/>
       <c r="B46" s="18"/>
       <c r="C46" s="20"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="19"/>
       <c r="B47" s="18"/>
       <c r="C47" s="20"/>
       <c r="F47" s="95"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="19"/>
       <c r="B48" s="18"/>
       <c r="C48" s="20"/>
     </row>
-    <row r="49" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="76" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B49" s="99"/>
       <c r="C49" s="100">
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="77"/>
       <c r="B50" s="77"/>
       <c r="C50" s="83"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="80" t="s">
         <v>4</v>
       </c>
@@ -1860,22 +1877,22 @@
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="18"/>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="18"/>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="18"/>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="18"/>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
@@ -1897,36 +1914,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" hidden="1" customWidth="1"/>
-    <col min="11" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="21"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="55" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="51">
-        <v>352133.83999999997</v>
+        <v>340968.94</v>
       </c>
       <c r="G1" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 15/09</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="106" t="str">
         <f>'detalle y gastos'!B7</f>
         <v>LIQUIDACIÓN EXPENSAS AGOSTO 2025</v>
@@ -1946,7 +1963,7 @@
       <c r="L2" s="101"/>
       <c r="M2" s="102"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="123"/>
       <c r="B3" s="121" t="s">
         <v>1</v>
@@ -1973,19 +1990,19 @@
         <v>7</v>
       </c>
       <c r="J3" s="131" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K3" s="125" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" s="125" t="s">
+        <v>83</v>
+      </c>
+      <c r="M3" s="125" t="s">
         <v>84</v>
       </c>
-      <c r="L3" s="125" t="s">
-        <v>85</v>
-      </c>
-      <c r="M3" s="125" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="124"/>
       <c r="B4" s="122"/>
       <c r="C4" s="129"/>
@@ -2000,7 +2017,7 @@
       <c r="L4" s="126"/>
       <c r="M4" s="126"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="103">
         <v>1</v>
       </c>
@@ -2011,14 +2028,14 @@
         <v>30</v>
       </c>
       <c r="D5" s="62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" s="47">
-        <v>38916.559659999992</v>
+        <v>42608.194639999994</v>
       </c>
       <c r="F5" s="120">
         <f t="shared" ref="F5:F11" si="0">E5</f>
-        <v>38916.559659999992</v>
+        <v>42608.194639999994</v>
       </c>
       <c r="G5" s="47">
         <f>E5-F5</f>
@@ -2034,18 +2051,18 @@
       <c r="J5" s="98"/>
       <c r="K5" s="110">
         <f>E1*I5</f>
-        <v>42608.194639999994</v>
+        <v>41257.241739999998</v>
       </c>
       <c r="L5" s="110">
         <f>E5-F5+H5+K5+J5</f>
-        <v>42608.194639999994</v>
+        <v>41257.241739999998</v>
       </c>
       <c r="M5" s="111">
         <f>L5+L5*4%</f>
-        <v>44312.522425599993</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>42907.5314096</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="103">
         <v>2</v>
       </c>
@@ -2056,14 +2073,14 @@
         <v>31</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="47">
-        <v>39238.184119999998</v>
+        <v>42960.328479999996</v>
       </c>
       <c r="F6" s="120">
         <f t="shared" si="0"/>
-        <v>39238.184119999998</v>
+        <v>42960.328479999996</v>
       </c>
       <c r="G6" s="47">
         <f t="shared" ref="G6:G12" si="1">E6-F6</f>
@@ -2079,20 +2096,20 @@
       <c r="J6" s="98"/>
       <c r="K6" s="110">
         <f>E1*I6</f>
-        <v>42960.328479999996</v>
+        <v>41598.210679999997</v>
       </c>
       <c r="L6" s="110">
         <f t="shared" ref="L6:L12" si="3">E6-F6+H6+K6+J6</f>
-        <v>42960.328479999996</v>
+        <v>41598.210679999997</v>
       </c>
       <c r="M6" s="111">
         <f t="shared" ref="M6:M12" si="4">L6+L6*4%</f>
-        <v>44678.741619199995</v>
+        <v>43262.139107199997</v>
       </c>
       <c r="O6" s="118"/>
       <c r="Q6" s="117"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="103">
         <v>3</v>
       </c>
@@ -2103,14 +2120,14 @@
         <v>32</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E7" s="47">
-        <v>37630.061819999995</v>
+        <v>41199.65928</v>
       </c>
       <c r="F7" s="120">
         <f t="shared" si="0"/>
-        <v>37630.061819999995</v>
+        <v>41199.65928</v>
       </c>
       <c r="G7" s="47">
         <f t="shared" si="1"/>
@@ -2126,18 +2143,18 @@
       <c r="J7" s="98"/>
       <c r="K7" s="110">
         <f>E1*I7</f>
-        <v>41199.65928</v>
+        <v>39893.365980000002</v>
       </c>
       <c r="L7" s="110">
         <f t="shared" si="3"/>
-        <v>41199.65928</v>
+        <v>39893.365980000002</v>
       </c>
       <c r="M7" s="111">
         <f t="shared" si="4"/>
-        <v>42847.6456512</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>41489.100619200006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="103">
         <v>4</v>
       </c>
@@ -2148,22 +2165,21 @@
         <v>33</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="E8" s="47">
-        <v>106362.93804998914</v>
+        <v>41199.65928</v>
       </c>
       <c r="F8" s="120">
-        <f t="shared" si="0"/>
-        <v>106362.93804998914</v>
+        <v>21423</v>
       </c>
       <c r="G8" s="47">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19776.65928</v>
       </c>
       <c r="H8" s="47">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>988.83296400000006</v>
       </c>
       <c r="I8" s="109">
         <v>0.11700000000000001</v>
@@ -2171,18 +2187,18 @@
       <c r="J8" s="98"/>
       <c r="K8" s="110">
         <f>E1*I8</f>
-        <v>41199.65928</v>
+        <v>39893.365980000002</v>
       </c>
       <c r="L8" s="110">
         <f t="shared" si="3"/>
-        <v>41199.65928</v>
+        <v>60658.858224000003</v>
       </c>
       <c r="M8" s="111">
         <f t="shared" si="4"/>
-        <v>42847.6456512</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+        <v>63085.212552960002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="103">
         <v>5</v>
       </c>
@@ -2193,18 +2209,17 @@
         <v>30</v>
       </c>
       <c r="D9" s="62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" s="47">
-        <v>44062.551019999999</v>
+        <v>48242.336080000001</v>
       </c>
       <c r="F9" s="120">
-        <f t="shared" si="0"/>
-        <v>44062.551019999999</v>
+        <v>48424.34</v>
       </c>
       <c r="G9" s="47">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-182.00391999999556</v>
       </c>
       <c r="H9" s="47">
         <f t="shared" si="2"/>
@@ -2216,18 +2231,18 @@
       <c r="J9" s="98"/>
       <c r="K9" s="110">
         <f>E1*I9</f>
-        <v>48242.336080000001</v>
+        <v>46712.744780000001</v>
       </c>
       <c r="L9" s="110">
         <f t="shared" si="3"/>
-        <v>48242.336080000001</v>
+        <v>46530.740860000005</v>
       </c>
       <c r="M9" s="111">
         <f t="shared" si="4"/>
-        <v>50172.029523199999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>48391.970494400004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="103">
         <v>6</v>
       </c>
@@ -2238,14 +2253,13 @@
         <v>30</v>
       </c>
       <c r="D10" s="62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" s="47">
-        <v>42454.428719999996</v>
+        <v>48341</v>
       </c>
       <c r="F10" s="120">
-        <f t="shared" si="0"/>
-        <v>42454.428719999996</v>
+        <v>48341</v>
       </c>
       <c r="G10" s="47">
         <f t="shared" si="1"/>
@@ -2261,18 +2275,18 @@
       <c r="J10" s="98"/>
       <c r="K10" s="110">
         <f>E1*I10</f>
-        <v>46481.666879999997</v>
+        <v>45007.900079999999</v>
       </c>
       <c r="L10" s="110">
         <f t="shared" si="3"/>
-        <v>46481.666879999997</v>
+        <v>45007.900079999999</v>
       </c>
       <c r="M10" s="111">
         <f t="shared" si="4"/>
-        <v>48340.933555199997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>46808.216083200001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="103">
         <v>7</v>
       </c>
@@ -2283,14 +2297,14 @@
         <v>32</v>
       </c>
       <c r="D11" s="62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E11" s="47">
-        <v>40846.306419999994</v>
+        <v>44720.997679999993</v>
       </c>
       <c r="F11" s="120">
         <f t="shared" si="0"/>
-        <v>40846.306419999994</v>
+        <v>44720.997679999993</v>
       </c>
       <c r="G11" s="47">
         <f t="shared" si="1"/>
@@ -2306,18 +2320,18 @@
       <c r="J11" s="98"/>
       <c r="K11" s="110">
         <f>E1*I11</f>
-        <v>44720.997679999993</v>
+        <v>43303.055379999998</v>
       </c>
       <c r="L11" s="110">
         <f t="shared" si="3"/>
-        <v>44720.997679999993</v>
+        <v>43303.055379999998</v>
       </c>
       <c r="M11" s="111">
         <f t="shared" si="4"/>
-        <v>46509.837587199996</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+        <v>45035.177595199995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="103">
         <v>8</v>
       </c>
@@ -2331,14 +2345,15 @@
         <v>61</v>
       </c>
       <c r="E12" s="47">
-        <v>39228.593219999995</v>
+        <v>41888.930899999985</v>
       </c>
       <c r="F12" s="120">
-        <v>42060.66</v>
+        <f>E12</f>
+        <v>41888.930899999985</v>
       </c>
       <c r="G12" s="47">
         <f t="shared" si="1"/>
-        <v>-2832.0667800000083</v>
+        <v>0</v>
       </c>
       <c r="H12" s="47">
         <f t="shared" si="2"/>
@@ -2350,18 +2365,18 @@
       <c r="J12" s="98"/>
       <c r="K12" s="110">
         <f>E1*I12</f>
-        <v>44720.997679999993</v>
+        <v>43303.055379999998</v>
       </c>
       <c r="L12" s="110">
         <f t="shared" si="3"/>
-        <v>41888.930899999985</v>
+        <v>43303.055379999998</v>
       </c>
       <c r="M12" s="111">
         <f t="shared" si="4"/>
-        <v>43564.488135999985</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>45035.177595199995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="112" t="s">
         <v>11</v>
       </c>
@@ -2370,16 +2385,16 @@
       <c r="D13" s="114"/>
       <c r="E13" s="115">
         <f>SUM(E5:E12)</f>
-        <v>388739.62302998907</v>
+        <v>351161.10633999994</v>
       </c>
       <c r="F13" s="104">
         <f>SUM(F5:F12)</f>
-        <v>391571.68980998907</v>
+        <v>331566.45097999997</v>
       </c>
       <c r="G13" s="104"/>
       <c r="H13" s="104">
         <f>SUM(H5:H12)</f>
-        <v>0</v>
+        <v>988.83296400000006</v>
       </c>
       <c r="I13" s="105">
         <f t="shared" ref="I13" si="5">SUM(I5:I12)</f>
@@ -2391,18 +2406,18 @@
       </c>
       <c r="K13" s="115">
         <f>SUM(K5:K12)</f>
-        <v>352133.83999999991</v>
+        <v>340968.93999999994</v>
       </c>
       <c r="L13" s="115">
         <f>SUM(L5:L12)</f>
-        <v>349301.77321999992</v>
+        <v>361552.42832399992</v>
       </c>
       <c r="M13" s="116">
         <f>SUM(M5:M12)</f>
-        <v>363273.84414880001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>376014.52545696002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="55" t="s">
         <v>53</v>
       </c>
@@ -2410,7 +2425,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
         <v>56</v>
       </c>
@@ -2429,7 +2444,7 @@
       <c r="L17" s="56"/>
       <c r="M17" s="32"/>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
@@ -2462,7 +2477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2489,7 +2504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>1</v>
       </c>
@@ -2524,7 +2539,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>2</v>
       </c>
@@ -2559,7 +2574,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>3</v>
       </c>
@@ -2595,7 +2610,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>4</v>
       </c>
@@ -2627,7 +2642,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>5</v>
       </c>
@@ -2659,7 +2674,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>6</v>
       </c>
@@ -2691,7 +2706,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>7</v>
       </c>
@@ -2726,7 +2741,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>8</v>
       </c>
@@ -2761,7 +2776,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>11</v>
       </c>
@@ -2795,15 +2810,15 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I30" s="60"/>
       <c r="J30" s="60"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I31" s="60"/>
       <c r="J31" s="60"/>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E39" s="54"/>
     </row>
   </sheetData>
@@ -2831,22 +2846,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="0.140625" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
     <col min="12" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D1" s="58">
         <v>50000</v>
       </c>
@@ -2856,16 +2871,16 @@
       <c r="I1" s="136"/>
       <c r="J1" s="136"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
         <v>53</v>
       </c>
       <c r="B2" s="1"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="30"/>
@@ -2886,7 +2901,7 @@
       <c r="N3" s="32"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2919,7 +2934,7 @@
       </c>
       <c r="K4" s="71"/>
       <c r="L4" s="134" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M4" s="81" t="s">
         <v>5</v>
@@ -2929,7 +2944,7 @@
       </c>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2950,17 +2965,17 @@
         <v>18</v>
       </c>
       <c r="J5" s="68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K5" s="61"/>
       <c r="L5" s="135"/>
       <c r="M5" s="82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N5" s="133"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -3008,7 +3023,7 @@
       </c>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>2</v>
       </c>
@@ -3056,7 +3071,7 @@
       </c>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>3</v>
       </c>
@@ -3104,7 +3119,7 @@
       </c>
       <c r="P8" s="21"/>
     </row>
-    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>4</v>
       </c>
@@ -3152,7 +3167,7 @@
       </c>
       <c r="P9" s="21"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>5</v>
       </c>
@@ -3200,7 +3215,7 @@
       </c>
       <c r="P10" s="21"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>6</v>
       </c>
@@ -3248,7 +3263,7 @@
       </c>
       <c r="P11" s="21"/>
     </row>
-    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>7</v>
       </c>
@@ -3296,7 +3311,7 @@
       </c>
       <c r="P12" s="21"/>
     </row>
-    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>8</v>
       </c>
@@ -3344,7 +3359,7 @@
       </c>
       <c r="P13" s="21"/>
     </row>
-    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
